--- a/Report/Demo_Bulk_Create_Students.xlsx
+++ b/Report/Demo_Bulk_Create_Students.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Học viên" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
+      <color rgb="001F497D"/>
       <sz val="13"/>
     </font>
     <font>
@@ -39,10 +39,10 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +51,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="00DCE6F1"/>
+        <bgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,35 +72,32 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,24 +467,24 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TẠO HÀNG LOẠT TÀI KHOẢN HỌC VIÊN (STUDENT)</t>
+          <t>BULK STUDENT ACCOUNTS CREATION</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Username (email)*</t>
@@ -489,37 +492,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu*</t>
+          <t>Password*</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Phòng ban (Department)*</t>
+          <t>Department*</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Họ và tên (FullName)*</t>
+          <t>FullName*</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ngày sinh (dd/MM/yyyy)</t>
+          <t>Date of Birth (dd/MM/yyyy)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Giới tính (Gender)</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Số điện thoại (Phone)</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Đơn vị/Tổ chức (Organization)</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -534,14 +537,14 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Lê Hoàng Nam</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Le Hoang Nam</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -551,7 +554,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -559,7 +562,7 @@
           <t>0987654301</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Cadet Pilot Batch 2026</t>
         </is>
@@ -576,14 +579,14 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Đặng Mai Linh</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Dang Mai Linh</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -593,7 +596,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -601,7 +604,7 @@
           <t>0987654302</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Cadet Pilot Batch 2026</t>
         </is>
@@ -618,14 +621,14 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Trần Minh Quân</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Tran Minh Quan</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -635,7 +638,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -643,7 +646,7 @@
           <t>0987654303</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Vietnam Airlines Trainee</t>
         </is>
@@ -660,14 +663,14 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Nguyễn Anh Tuấn</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Nguyen Anh Tuan</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -677,7 +680,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -685,7 +688,7 @@
           <t>0987654304</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Vietjet Air Trainee</t>
         </is>
@@ -702,14 +705,14 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Hoàng Bảo Ngọc</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Hoang Bao Ngoc</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -719,7 +722,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -727,7 +730,7 @@
           <t>0987654305</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Cadet Pilot Batch 2026</t>
         </is>
